--- a/branches/feat/comparison-toggle/StructureDefinition-example-patient.xlsx
+++ b/branches/feat/comparison-toggle/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T18:49:08+00:00</t>
+    <t>2026-07-30T18:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/comparison-toggle/StructureDefinition-example-patient.xlsx
+++ b/branches/feat/comparison-toggle/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T18:54:10+00:00</t>
+    <t>2026-07-30T19:02:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
